--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER - Copia.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER - Copia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{062D9DE4-293B-4263-BA42-5DF3761B4283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E6A752-33AA-4E45-91F8-7A01E42DE8C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="12">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,88 +54,16 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander -14/10/2025</t>
+    <t>Relatório de Recusas Santander -17, 18 e 20/10/2025</t>
   </si>
   <si>
-    <t>134805081</t>
-  </si>
-  <si>
-    <t>134795918</t>
-  </si>
-  <si>
-    <t>134723692</t>
-  </si>
-  <si>
-    <t>134844875</t>
-  </si>
-  <si>
-    <t>134859553</t>
-  </si>
-  <si>
-    <t>134863856</t>
-  </si>
-  <si>
-    <t>134882456</t>
-  </si>
-  <si>
-    <t>134908363</t>
-  </si>
-  <si>
-    <t>134910576</t>
-  </si>
-  <si>
-    <t>134731932</t>
-  </si>
-  <si>
-    <t>134765346</t>
-  </si>
-  <si>
-    <t>134676156</t>
-  </si>
-  <si>
-    <t>134723777</t>
-  </si>
-  <si>
-    <t>134917403</t>
-  </si>
-  <si>
-    <t>134765510</t>
-  </si>
-  <si>
-    <t>134864443</t>
-  </si>
-  <si>
-    <t>134705316</t>
-  </si>
-  <si>
-    <t>134726860</t>
-  </si>
-  <si>
-    <t>134795689</t>
-  </si>
-  <si>
-    <t>134796301</t>
-  </si>
-  <si>
-    <t>134796722</t>
-  </si>
-  <si>
-    <t>134796877</t>
-  </si>
-  <si>
-    <t>134798453</t>
-  </si>
-  <si>
-    <t>134798705</t>
-  </si>
-  <si>
-    <t>134800611</t>
-  </si>
-  <si>
-    <t>134802251</t>
+    <t>Relatório de Recusas 20.10.2025 a 26.10.2025</t>
   </si>
   <si>
     <t>Relatório de Recusas 13.10.2025 a 19.10.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas Santander - 20/10/2025</t>
   </si>
 </sst>
 </file>
@@ -165,8 +93,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -191,7 +119,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -199,11 +127,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -220,7 +178,13 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -540,7 +504,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F133"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -572,16 +536,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134734284</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
+        <v>134826721</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -589,17 +553,17 @@
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="A3" s="6">
+        <v>134838938</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -607,17 +571,17 @@
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="A4" s="6">
+        <v>134838645</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -625,17 +589,17 @@
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="A5" s="6">
+        <v>134869500</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -643,17 +607,17 @@
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="A6" s="6">
+        <v>134910944</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -661,17 +625,17 @@
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="A7" s="6">
+        <v>134929230</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -679,17 +643,17 @@
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="A8" s="6">
+        <v>134933777</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -697,17 +661,17 @@
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="A9" s="6">
+        <v>134966232</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -715,17 +679,17 @@
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="A10" s="6">
+        <v>134964144</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -733,17 +697,17 @@
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="A11" s="6">
+        <v>134860076</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -751,17 +715,17 @@
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="A12" s="6">
+        <v>134869548</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -769,17 +733,17 @@
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="A13" s="6">
+        <v>134988983</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -787,17 +751,17 @@
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="A14" s="6">
+        <v>134839437</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -805,17 +769,17 @@
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="A15" s="6">
+        <v>134842546</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -823,17 +787,17 @@
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="A16" s="6">
+        <v>134844371</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -841,17 +805,17 @@
       <c r="F16"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="A17" s="6">
+        <v>134847539</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -859,17 +823,17 @@
       <c r="F17"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="A18" s="6">
+        <v>134847996</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -877,17 +841,17 @@
       <c r="F18"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="A19" s="6">
+        <v>134849889</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -895,17 +859,17 @@
       <c r="F19"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="A20" s="6">
+        <v>134852830</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -913,17 +877,17 @@
       <c r="F20"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="A21" s="6">
+        <v>134854093</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -931,17 +895,17 @@
       <c r="F21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="A22" s="6">
+        <v>134854982</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -949,106 +913,1557 @@
       <c r="F22"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="A23" s="6">
+        <v>134857172</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="A24" s="6">
+        <v>134860535</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="A25" s="6">
+        <v>134813625</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="A26" s="6">
+        <v>134814178</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="A27" s="6">
+        <v>134814240</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
+      <c r="A28" s="6">
+        <v>134814818</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
       </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="6">
+        <v>134818587</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
+        <v>134818815</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <v>134878294</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="6">
+        <v>134893359</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
+        <v>134881062</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <v>134874668</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="6">
+        <v>134891446</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="6">
+        <v>134826952</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="6">
+        <v>134876679</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="6">
+        <v>134920718</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <v>134926193</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <v>134927129</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="6">
+        <v>134924632</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="6">
+        <v>134943152</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="6">
+        <v>134946354</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="6">
+        <v>134948123</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="6">
+        <v>134946767</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="6">
+        <v>134954190</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
+        <v>134948164</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
+        <v>134899850</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="6">
+        <v>134980185</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="6">
+        <v>134926575</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
+        <v>134912411</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
+        <v>134933365</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="6">
+        <v>134923813</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="6">
+        <v>134873058</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="6">
+        <v>134934767</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="6">
+        <v>134826721</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="6">
+        <v>134838938</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="6">
+        <v>134838645</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="6">
+        <v>134869500</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="6">
+        <v>134910944</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="6">
+        <v>134929230</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="6">
+        <v>134933777</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="6">
+        <v>134966232</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="6">
+        <v>134964144</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="6">
+        <v>134860076</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="6">
+        <v>134869548</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="6">
+        <v>134988983</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="6">
+        <v>134839437</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="6">
+        <v>134842546</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="6">
+        <v>134844371</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="6">
+        <v>134847539</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="6">
+        <v>134847996</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="6">
+        <v>134849889</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="6">
+        <v>134852830</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="6">
+        <v>134854093</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="6">
+        <v>134854982</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="6">
+        <v>134857172</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="6">
+        <v>134860535</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="6">
+        <v>134813625</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="6">
+        <v>134814178</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="6">
+        <v>134814240</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="6">
+        <v>134814818</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="6">
+        <v>134818587</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="6">
+        <v>134818815</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="6">
+        <v>134878294</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="6">
+        <v>134893359</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D86" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="6">
+        <v>134881062</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="6">
+        <v>134874668</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="6">
+        <v>134891446</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D89" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="6">
+        <v>134826952</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D90" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="6">
+        <v>134876679</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="6">
+        <v>134920718</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D92" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="6">
+        <v>134926193</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="6">
+        <v>134927129</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D94" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="6">
+        <v>134924632</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="6">
+        <v>134943152</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D96" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="6">
+        <v>134946354</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="6">
+        <v>134948123</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D98" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="6">
+        <v>134946767</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D99" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="6">
+        <v>134954190</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D100" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="6">
+        <v>134948164</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D101" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="6">
+        <v>134899850</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D102" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="6">
+        <v>134980185</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D103" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="6">
+        <v>134926575</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D104" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="6">
+        <v>134912411</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D105" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="6">
+        <v>134933365</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D106" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="6">
+        <v>134923813</v>
+      </c>
+      <c r="B107" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D107" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="6">
+        <v>134873058</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C108" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D108" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="6">
+        <v>134934767</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C109" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D109" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C110" s="8"/>
+      <c r="D110" s="8"/>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C111" s="8"/>
+      <c r="D111" s="8"/>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D112" s="8"/>
+    </row>
+    <row r="113" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D113" s="8"/>
+    </row>
+    <row r="114" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D114" s="8"/>
+    </row>
+    <row r="115" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D115" s="8"/>
+    </row>
+    <row r="116" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D116" s="8"/>
+    </row>
+    <row r="117" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D117" s="8"/>
+    </row>
+    <row r="118" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D118" s="8"/>
+    </row>
+    <row r="119" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D119" s="8"/>
+    </row>
+    <row r="120" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D120" s="8"/>
+    </row>
+    <row r="121" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D121" s="8"/>
+    </row>
+    <row r="122" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D122" s="8"/>
+    </row>
+    <row r="123" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D123" s="8"/>
+    </row>
+    <row r="124" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D124" s="8"/>
+    </row>
+    <row r="125" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D125" s="8"/>
+    </row>
+    <row r="126" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D126" s="8"/>
+    </row>
+    <row r="127" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D127" s="8"/>
+    </row>
+    <row r="128" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D128" s="8"/>
+    </row>
+    <row r="129" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D129" s="8"/>
+    </row>
+    <row r="130" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D130" s="8"/>
+    </row>
+    <row r="131" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D131" s="8"/>
+    </row>
+    <row r="132" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D132" s="8"/>
+    </row>
+    <row r="133" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D133" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
